--- a/ozone/multistate/ozone_VTZP_MS_3_70_30_SHAP.xlsx
+++ b/ozone/multistate/ozone_VTZP_MS_3_70_30_SHAP.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0006234025500108783</v>
+        <v>0.0006426450267980508</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0005247365421201665</v>
+        <v>0.0005523616938512779</v>
       </c>
     </row>
     <row r="4">
@@ -476,20 +476,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0005143769566250845</v>
+        <v>0.0005133513747589599</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$(\eta_{p})_{3}$</t>
+          <t>$(F_{p})_{3}$</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0004019142631869382</v>
+        <v>0.0003582525838717237</v>
       </c>
     </row>
     <row r="6">
@@ -502,46 +502,46 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0002992246701063444</v>
+        <v>0.0003259551523492294</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$\langle qq \vert qq \rangle$</t>
+          <t>h$_{s}$</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0002848353719860913</v>
+        <v>0.000257879065142566</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$(F_{p})_{3}$</t>
+          <t>$(\eta_{p})_{3}$</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0002636598107636139</v>
+        <v>0.0002531631704881275</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>h$_{s}$</t>
+          <t>$\langle qq \vert qq \rangle$</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.000252175209257103</v>
+        <v>0.0002498092470838845</v>
       </c>
     </row>
     <row r="10">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0002444878862752335</v>
+        <v>0.0002300933584428194</v>
       </c>
     </row>
     <row r="11">
@@ -567,46 +567,46 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0002161535541380814</v>
+        <v>0.0002255254394604048</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>$F_{s}$</t>
+          <t>$(F_{p}^{\text{SCF}})_{3}$</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0002053940069953858</v>
+        <v>0.0001954069802551851</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>h$_{q}$</t>
+          <t>$(\langle rr \vert rr \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0001954066183068242</v>
+        <v>0.0001935524319485686</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$(\langle rr \vert rr \rangle)_{1}$</t>
+          <t>$F_{s}$</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.000186231359426187</v>
+        <v>0.0001768169845687384</v>
       </c>
     </row>
     <row r="15">
@@ -619,111 +619,111 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.00017408825621719</v>
+        <v>0.0001719429168988397</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>$(F_{p}^{\text{SCF}})_{3}$</t>
+          <t>h$_{qs}$</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0001690997338695268</v>
+        <v>0.0001715481541620305</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>(h$_{p}$)$_{3}$</t>
+          <t>(h$_{r}$)$_{0}$</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0001500455239105638</v>
+        <v>0.0001673115857498048</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>(h$_{r}$)$_{0}$</t>
+          <t>h$_{q}$</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0001472806226306859</v>
+        <v>0.000148105752342398</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>h$_{qs}$</t>
+          <t>$type_1$</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0001374635864189339</v>
+        <v>0.0001314310929834926</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$type_1$</t>
+          <t>$F_{q}$</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0001334315510690292</v>
+        <v>0.000130128499976845</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>(h$_{r}$)$_{3}$</t>
+          <t>(h$_{p}$)$_{3}$</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0001221678952734506</v>
+        <v>0.00012789769869481</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>(h$_{r}$)$_{1}$</t>
+          <t>$(\langle rr \vert rr \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0001148757373093933</v>
+        <v>0.0001254881618524233</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>$(\langle rr \vert rr \rangle)_{2}$</t>
+          <t>(h$_{r}$)$_{1}$</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0001135280099886876</v>
+        <v>9.909868661843795e-05</v>
       </c>
     </row>
     <row r="24">
@@ -736,20 +736,20 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8.869316016766467e-05</v>
+        <v>8.962261711440366e-05</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert pq \rangle)_{2}$</t>
+          <t>$(F_{p})_{2}$</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.492784164802038e-05</v>
+        <v>8.510657536137429e-05</v>
       </c>
     </row>
     <row r="26">
@@ -762,72 +762,72 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8.428032718997177e-05</v>
+        <v>8.274645144605068e-05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>$(F_{r}^{\text{SCF}})_{3}$</t>
+          <t>$(\langle pq \vert pq \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7.915151684028413e-05</v>
+        <v>8.083200201512346e-05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>$F_{q}$</t>
+          <t>$(F_{r}^{\text{SCF}})_{3}$</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7.143529350564074e-05</v>
+        <v>8.021063807284241e-05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>$(\langle rs \vert sr \rangle)_{3}$</t>
+          <t>(h$_{r}$)$_{3}$</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.968482856034737e-05</v>
+        <v>7.846337084204611e-05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>$(F_{p})_{2}$</t>
+          <t>(h$_{rs}$)$_{2}$</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.63777095395635e-05</v>
+        <v>7.634889983650761e-05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>(h$_{rs}$)$_{2}$</t>
+          <t>$type_3$</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6.604116910286387e-05</v>
+        <v>6.932937797388087e-05</v>
       </c>
     </row>
     <row r="32">
@@ -840,826 +840,826 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6.508760666729726e-05</v>
+        <v>6.755584450608766e-05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>$(\langle rs\vert rs \rangle)_{2}$</t>
+          <t>$(\langle rs \vert sr \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.046892788966209e-05</v>
+        <v>6.666952293424844e-05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>$(\eta_{r})_{1}$</t>
+          <t>$(\langle rs\vert rs \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5.724362928531675e-05</v>
+        <v>6.425024600404915e-05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>$(\langle rr \vert rr \rangle)_{3}$</t>
+          <t>$(F_{p}^{\text{SCF}})_{2}$</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5.642814809743018e-05</v>
+        <v>6.138671036265135e-05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>$(\langle rs\vert rs \rangle)_{3}$</t>
+          <t>$(\langle pp \vert pp \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5.440850512680293e-05</v>
+        <v>6.029933658529086e-05</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert qp \rangle)_{3}$</t>
+          <t>$(\langle rs\vert rs \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4.992671648540917e-05</v>
+        <v>5.712288895327687e-05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>(h$_{p}$)$_{0}$</t>
+          <t>$(\langle pq \vert qp \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.793261702836491e-05</v>
+        <v>5.654171684767937e-05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>$(F_{p}^{\text{SCF}})_{2}$</t>
+          <t>(h$_{p}$)$_{0}$</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4.700336611429385e-05</v>
+        <v>5.241691566099494e-05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>$(F_{p}^{\text{SCF}})_{1}$</t>
+          <t>(h$_{p}$)$_{2}$</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4.478557224151146e-05</v>
+        <v>5.222574466467236e-05</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert rs \rangle)_{2}$</t>
+          <t>$(F_{r})_{3}$</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4.381632807355112e-05</v>
+        <v>4.677610405356746e-05</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert rs \rangle)_{3}$</t>
+          <t>$(\langle rr \vert rr \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4.19113360958937e-05</v>
+        <v>4.557311872979027e-05</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>(h$_{rs}$)$_{3}$</t>
+          <t>$(\langle pq \vert rs \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4.182669934539626e-05</v>
+        <v>4.370226428458031e-05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>(h$_{p}$)$_{2}$</t>
+          <t>$(\langle pp \vert pp \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.095819934952624e-05</v>
+        <v>4.365832887797928e-05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>$(\langle pp \vert pp \rangle)_{3}$</t>
+          <t>$(\langle rs \vert sr \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4.035427871917422e-05</v>
+        <v>4.326159143268347e-05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>$(\langle pp \vert pp \rangle)_{1}$</t>
+          <t>$(\langle rs \vert sr \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3.732261778572222e-05</v>
+        <v>4.152411951527199e-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>$(\langle rs \vert sr \rangle)_{2}$</t>
+          <t>$(\eta_{r})_{1}$</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3.591720667043433e-05</v>
+        <v>4.024320499496233e-05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert pq \rangle)_{1}$</t>
+          <t>$(\langle pp \vert pp \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3.587949886345144e-05</v>
+        <v>3.796025971960447e-05</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>$(\langle rs \vert sr \rangle)_{1}$</t>
+          <t>$(F_{r}^{\text{SCF}})_{2}$</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3.576709183676132e-05</v>
+        <v>3.725249269128695e-05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>$type_0$</t>
+          <t>$(F_{p})_{0}$</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3.567034870582801e-05</v>
+        <v>3.597809373715336e-05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>$(\langle rs\vert rs \rangle)_{0}$</t>
+          <t>$(F_{p}^{\text{SCF}})_{0}$</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3.410820814613785e-05</v>
+        <v>3.498117610655735e-05</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert qp \rangle)_{0}$</t>
+          <t>$(F_{r}^{\text{SCF}})_{1}$</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3.354309725812606e-05</v>
+        <v>3.443003932549887e-05</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>(h$_{pq}$)$_{1}$</t>
+          <t>$(\langle pq \vert qp \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3.352264531764427e-05</v>
+        <v>3.313073940131587e-05</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>$(F_{r}^{\text{SCF}})_{1}$</t>
+          <t>(h$_{rs}$)$_{3}$</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3.32388026424611e-05</v>
+        <v>3.297735333157522e-05</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>$(F_{r})_{3}$</t>
+          <t>$(\langle rs\vert rs \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3.226181234302092e-05</v>
+        <v>3.297210221360701e-05</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>$(\langle rs\vert rs \rangle)_{1}$</t>
+          <t>(h$_{pq}$)$_{3}$</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3.220491250043626e-05</v>
+        <v>3.231608863625722e-05</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>$(\langle rs \vert sr \rangle)_{0}$</t>
+          <t>$(\langle pq \vert rs \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3.132219706290185e-05</v>
+        <v>3.031018942790849e-05</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>(h$_{pq}$)$_{3}$</t>
+          <t>$(\langle pq \vert pq \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3.096172678372985e-05</v>
+        <v>3.002299891896885e-05</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>(h$_{rs}$)$_{1}$</t>
+          <t>(h$_{pr}$)$_{0}$</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3.08623573206885e-05</v>
+        <v>2.986360272034496e-05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>$(\langle pp \vert pp \rangle)_{2}$</t>
+          <t>$(F_{p}^{\text{SCF}})_{1}$</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3.004206962446382e-05</v>
+        <v>2.930609344533478e-05</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>(h$_{pr}$)$_{0}$</t>
+          <t>$(\eta_{r})_{3}$</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2.912637252641308e-05</v>
+        <v>2.833624896904638e-05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>$type_3$</t>
+          <t>$type_0$</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2.666532648379138e-05</v>
+        <v>2.802638248628102e-05</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>$(F_{r}^{\text{SCF}})_{2}$</t>
+          <t>$(\langle rs \vert sr \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2.509058755045469e-05</v>
+        <v>2.684145031810158e-05</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>$(F_{p})_{1}$</t>
+          <t>(h$_{pq}$)$_{1}$</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2.506130094259909e-05</v>
+        <v>2.63318373555938e-05</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>$(\langle pp \vert pp \rangle)_{0}$</t>
+          <t>(h$_{rs}$)$_{1}$</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2.415168214188254e-05</v>
+        <v>2.537107803289587e-05</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>(h$_{pr}$)$_{2}$</t>
+          <t>$(\langle pq \vert qp \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2.255309225338423e-05</v>
+        <v>2.528020833001317e-05</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>(h$_{r}$)$_{2}$</t>
+          <t>(h$_{pr}$)$_{3}$</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2.245444526598492e-05</v>
+        <v>2.487084071474779e-05</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert qp \rangle)_{1}$</t>
+          <t>$(\langle pp \vert pp \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2.214160310046346e-05</v>
+        <v>2.475074961345018e-05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>$(\eta_{r})_{3}$</t>
+          <t>(h$_{pr}$)$_{2}$</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2.192591322977192e-05</v>
+        <v>2.343261073219787e-05</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>(h$_{pr}$)$_{3}$</t>
+          <t>(h$_{pq}$)$_{0}$</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.873149112756643e-05</v>
+        <v>2.2548992443582e-05</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>(h$_{pq}$)$_{0}$</t>
+          <t>(h$_{r}$)$_{2}$</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.819001968505094e-05</v>
+        <v>2.159814155439596e-05</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>$(F_{p})_{0}$</t>
+          <t>$(\langle rs\vert rs \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1.790547209894745e-05</v>
+        <v>2.087599813515522e-05</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>(h$_{pq}$)$_{2}$</t>
+          <t>(h$_{pr}$)$_{1}$</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1.642544647309307e-05</v>
+        <v>2.059691815847344e-05</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>$(F_{r}^{\text{SCF}})_{0}$</t>
+          <t>(h$_{rs}$)$_{0}$</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1.535269605841919e-05</v>
+        <v>1.843506714629895e-05</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>(h$_{rs}$)$_{0}$</t>
+          <t>$(\langle pq \vert sr \rangle)_{3}$</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1.446088615520231e-05</v>
+        <v>1.56504037442497e-05</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>$(\langle rr \vert rr \rangle)_{0}$</t>
+          <t>(h$_{pq}$)$_{2}$</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1.377075210864468e-05</v>
+        <v>1.513591844992467e-05</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>$(F_{r})_{1}$</t>
+          <t>$(F_{r})_{2}$</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.26052095647128e-05</v>
+        <v>1.478285160971195e-05</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>$(F_{r})_{0}$</t>
+          <t>$(F_{p})_{1}$</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.190099512907598e-05</v>
+        <v>1.4346750452197e-05</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert rs \rangle)_{1}$</t>
+          <t>$(\langle pq \vert rs \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1.13188775860018e-05</v>
+        <v>1.424375423098557e-05</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>$(F_{r})_{2}$</t>
+          <t>$(\langle pq \vert sr \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.117086761022324e-05</v>
+        <v>1.417930311805581e-05</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert rs \rangle)_{0}$</t>
+          <t>$(\langle pq \vert sr \rangle)_{2}$</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1.091459401220204e-05</v>
+        <v>1.358050650020239e-05</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>$(F_{p}^{\text{SCF}})_{0}$</t>
+          <t>$(F_{r})_{1}$</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1.042864231087635e-05</v>
+        <v>1.322095668162271e-05</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>(h$_{pr}$)$_{1}$</t>
+          <t>$(\eta_{p})_{2}$</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9.754806082604816e-06</v>
+        <v>1.217315928491026e-05</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>$(\eta_{r})_{2}$</t>
+          <t>$(\langle rr \vert rr \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>9.584796268066281e-06</v>
+        <v>1.061768095262946e-05</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>$(\eta_{r})_{0}$</t>
+          <t>$(\langle pq \vert sr \rangle)_{0}$</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>8.342185483403167e-06</v>
+        <v>9.766486045107913e-06</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>$\mathbf{b}$</t>
+          <t>$(\eta_{r})_{2}$</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5.554511166643136e-06</v>
+        <v>9.660588312639428e-06</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>$\omega_{q}$</t>
+          <t>$(\langle pq \vert rs \rangle)_{1}$</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4.00894661777089e-06</v>
+        <v>6.770430620763163e-06</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>$(\eta_{p})_{1}$</t>
+          <t>$(F_{r}^{\text{SCF}})_{0}$</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2.506341481979579e-06</v>
+        <v>6.44865525246201e-06</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>$(\eta_{p})_{2}$</t>
+          <t>$(F_{r})_{0}$</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1.500735597736873e-06</v>
+        <v>6.275299981965929e-06</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>$(\eta_{p})_{0}$</t>
+          <t>$(\eta_{r})_{0}$</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1.02064196914861e-06</v>
+        <v>3.672279783031318e-06</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>$(\omega_{r})_{1}$</t>
+          <t>$(\eta_{p})_{0}$</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>5.97587117885499e-08</v>
+        <v>1.276959668628279e-06</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>$(\omega_{r})_{3}$</t>
+          <t>$(\eta_{p})_{1}$</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5.726388497799765e-08</v>
+        <v>6.19385751940409e-07</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert sr \rangle)_{0}$</t>
+          <t>$(\omega_{r})_{3}$</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5.436710050350185e-08</v>
+        <v>7.660498160382466e-08</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>$\omega_{s}$</t>
+          <t>$(\omega_{r})_{2}$</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5.395499298827729e-08</v>
+        <v>7.517018386883308e-08</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert sr \rangle)_{3}$</t>
+          <t>$(\omega_{r})_{1}$</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5.383728868715099e-08</v>
+        <v>7.321222460264639e-08</v>
       </c>
     </row>
     <row r="96">
@@ -1672,20 +1672,20 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5.369063228460226e-08</v>
+        <v>5.971370314947998e-08</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>$(\omega_{r})_{2}$</t>
+          <t>$\omega_{s}$</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>5.348851797574382e-08</v>
+        <v>5.805208687200925e-08</v>
       </c>
     </row>
     <row r="98">
@@ -1698,33 +1698,33 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>5.007752377047556e-08</v>
+        <v>5.537357066813845e-08</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert sr \rangle)_{1}$</t>
+          <t>$(\omega_{p})_{0}$</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4.966597187044748e-08</v>
+        <v>4.467144832849964e-08</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>$(\langle pq \vert sr \rangle)_{2}$</t>
+          <t>$\omega_{q}$</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4.496376143838741e-08</v>
+        <v>4.369785190447639e-08</v>
       </c>
     </row>
     <row r="101">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4.21063207540796e-08</v>
+        <v>3.919811605901499e-08</v>
       </c>
     </row>
     <row r="102">
@@ -1750,20 +1750,20 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4.022120220111862e-08</v>
+        <v>3.589004889906997e-08</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>$(\omega_{p})_{0}$</t>
+          <t>$\mathbf{b}$</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3.572030148040216e-08</v>
+        <v>2.208387504494742e-08</v>
       </c>
     </row>
   </sheetData>
